--- a/artfynd/A 27944-2026 artfynd.xlsx
+++ b/artfynd/A 27944-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AZ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134964336</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969822</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970243</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959317</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965685</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967364</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955487</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955663</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960026</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963920</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969433</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955884</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956944</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959509</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965686</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969054</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970453</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955490</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956946</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958067</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958273</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959318</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965062</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966524</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967591</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968013</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968214</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959112</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959726</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966741</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955915</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3781,6 +3941,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960228</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3883,6 +4048,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958704</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3980,6 +4150,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969047</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4077,6 +4252,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967789</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4174,6 +4354,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134962877</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4280,6 +4465,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134964116</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4386,6 +4576,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965681</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4488,6 +4683,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969824</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4585,6 +4785,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956943</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4687,6 +4892,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967362</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4788,6 +4998,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956313</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4885,6 +5100,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968015</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4986,6 +5206,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134971311</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5087,6 +5312,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134961306</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5184,6 +5414,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968637</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5281,6 +5516,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134964824</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5378,6 +5618,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956545</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5475,6 +5720,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958916</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5576,6 +5826,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134957861</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5673,6 +5928,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960444</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5774,6 +6034,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960660</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5875,6 +6140,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134962674</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5976,6 +6246,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965060</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6077,6 +6352,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965469</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6178,6 +6458,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966321</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6279,6 +6564,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968215</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6380,6 +6670,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968425</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6481,6 +6776,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969826</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6582,6 +6882,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970656</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6679,6 +6984,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959512</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6776,6 +7086,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134964335</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6873,6 +7188,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134957161</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6970,6 +7290,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969052</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7067,6 +7392,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134961965</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7164,6 +7494,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960446</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7261,6 +7596,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960657</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7358,6 +7698,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955446</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7455,6 +7800,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968423</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7552,6 +7902,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969050</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7649,6 +8004,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967592</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7746,6 +8106,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959723</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7843,8 +8208,88 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134961970</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27944-2026 artfynd.xlsx
+++ b/artfynd/A 27944-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134964336</v>
       </c>
       <c r="B2" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>134969822</v>
       </c>
       <c r="B3" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>134970243</v>
       </c>
       <c r="B4" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>134959317</v>
       </c>
       <c r="B5" t="n">
-        <v>97262</v>
+        <v>97306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>134965685</v>
       </c>
       <c r="B6" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>134967364</v>
       </c>
       <c r="B7" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>134955487</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>134955663</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>134960026</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>134963920</v>
       </c>
       <c r="B11" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>134969433</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>134955884</v>
       </c>
       <c r="B13" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>134956944</v>
       </c>
       <c r="B14" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>134959509</v>
       </c>
       <c r="B15" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>134965686</v>
       </c>
       <c r="B16" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>134969054</v>
       </c>
       <c r="B17" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>134970453</v>
       </c>
       <c r="B18" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>134955490</v>
       </c>
       <c r="B19" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>134956946</v>
       </c>
       <c r="B20" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>134958067</v>
       </c>
       <c r="B21" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>134958273</v>
       </c>
       <c r="B22" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>134959318</v>
       </c>
       <c r="B23" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>134965062</v>
       </c>
       <c r="B24" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>134966524</v>
       </c>
       <c r="B25" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>134967591</v>
       </c>
       <c r="B26" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>134968013</v>
       </c>
       <c r="B27" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>134968214</v>
       </c>
       <c r="B28" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>134959112</v>
       </c>
       <c r="B29" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>134959726</v>
       </c>
       <c r="B30" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>134966741</v>
       </c>
       <c r="B31" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>134955915</v>
       </c>
       <c r="B32" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>134960228</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>134958704</v>
       </c>
       <c r="B34" t="n">
-        <v>57153</v>
+        <v>57158</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>134969047</v>
       </c>
       <c r="B35" t="n">
-        <v>57153</v>
+        <v>57158</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>134967789</v>
       </c>
       <c r="B36" t="n">
-        <v>57165</v>
+        <v>57170</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>134962877</v>
       </c>
       <c r="B37" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>134964116</v>
       </c>
       <c r="B38" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>134965681</v>
       </c>
       <c r="B39" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>134969824</v>
       </c>
       <c r="B40" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>134956943</v>
       </c>
       <c r="B41" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>134967362</v>
       </c>
       <c r="B42" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>134956313</v>
       </c>
       <c r="B43" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>134968015</v>
       </c>
       <c r="B44" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>134971311</v>
       </c>
       <c r="B45" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>134961306</v>
       </c>
       <c r="B46" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>134968637</v>
       </c>
       <c r="B47" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>134964824</v>
       </c>
       <c r="B48" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>134956545</v>
       </c>
       <c r="B49" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>134958916</v>
       </c>
       <c r="B50" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>134957861</v>
       </c>
       <c r="B51" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>134960444</v>
       </c>
       <c r="B52" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>134960660</v>
       </c>
       <c r="B53" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>134962674</v>
       </c>
       <c r="B54" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>134965060</v>
       </c>
       <c r="B55" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>134965469</v>
       </c>
       <c r="B56" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>134966321</v>
       </c>
       <c r="B57" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>134968215</v>
       </c>
       <c r="B58" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>134968425</v>
       </c>
       <c r="B59" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>134969826</v>
       </c>
       <c r="B60" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>134970656</v>
       </c>
       <c r="B61" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>134959512</v>
       </c>
       <c r="B62" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>134964335</v>
       </c>
       <c r="B63" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>134957161</v>
       </c>
       <c r="B64" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>134969052</v>
       </c>
       <c r="B65" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>134961965</v>
       </c>
       <c r="B66" t="n">
-        <v>98063</v>
+        <v>98107</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>134960446</v>
       </c>
       <c r="B67" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>134960657</v>
       </c>
       <c r="B68" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>134955446</v>
       </c>
       <c r="B69" t="n">
-        <v>98277</v>
+        <v>98321</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>134968423</v>
       </c>
       <c r="B70" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>134969050</v>
       </c>
       <c r="B71" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>134967592</v>
       </c>
       <c r="B72" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>134959723</v>
       </c>
       <c r="B73" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>134961970</v>
       </c>
       <c r="B74" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
